--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendrapisal/rei/govgrants-product-automation/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09959F57-D600-2E4A-831D-215F6EF1B2DA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B34585-930B-4D88-87BA-616B39194AAC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="23260" windowHeight="12580" activeTab="2" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="85">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -84,9 +84,6 @@
     <t>Budget</t>
   </si>
   <si>
-    <t>SubmittedOnForm__c</t>
-  </si>
-  <si>
     <t>Question1__c</t>
   </si>
   <si>
@@ -132,9 +129,6 @@
     <t>Justified</t>
   </si>
   <si>
-    <t>AppplicationSubmitted__c</t>
-  </si>
-  <si>
     <t>Execution Announcement for Automation</t>
   </si>
   <si>
@@ -286,13 +280,22 @@
   </si>
   <si>
     <t>City__c</t>
+  </si>
+  <si>
+    <t>fieldAutomation SPI2</t>
+  </si>
+  <si>
+    <t>fieldSubmittedOnForm__c</t>
+  </si>
+  <si>
+    <t>fieldAppplicationSubmitted__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -669,14 +672,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -687,59 +690,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" t="s">
         <v>70</v>
       </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
         <v>69</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -751,13 +754,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -765,7 +768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -773,7 +776,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -781,27 +784,27 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -820,13 +823,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,59 +840,59 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
         <v>76</v>
       </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
         <v>77</v>
       </c>
-      <c r="C4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" t="s">
-        <v>79</v>
-      </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -900,13 +903,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -917,26 +920,26 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -948,13 +951,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -965,147 +968,147 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>40</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>43</v>
       </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>44</v>
       </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
         <v>45</v>
       </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
         <v>46</v>
       </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>48</v>
-      </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1116,14 +1119,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1134,133 +1137,133 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>51</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>52</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
         <v>54</v>
-      </c>
-      <c r="C5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="B10" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
       </c>
       <c r="C10">
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
         <v>60</v>
-      </c>
-      <c r="B11" t="s">
-        <v>62</v>
       </c>
       <c r="C11">
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C13">
         <v>100000</v>
@@ -1277,13 +1280,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1294,7 +1297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1302,7 +1305,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1313,13 +1316,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1330,26 +1333,26 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1361,13 +1364,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1378,70 +1381,70 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
         <v>76</v>
       </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
         <v>77</v>
       </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1453,13 +1456,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1470,125 +1473,125 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>26</v>
       </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5944B40F-62D7-4C32-AB75-50954A932778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093CC3BA-5D8A-4100-9F68-01A898F6AD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="82">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -252,24 +252,6 @@
     <t>Agreement5__c</t>
   </si>
   <si>
-    <t>fieldAcknowledgment4__c</t>
-  </si>
-  <si>
-    <t>fieldProjectAbstract__c</t>
-  </si>
-  <si>
-    <t>fieldJustification__c</t>
-  </si>
-  <si>
-    <t>fieldApproachMethodology__c</t>
-  </si>
-  <si>
-    <t>fieldCapacity__c</t>
-  </si>
-  <si>
-    <t>fieldQualifications__c</t>
-  </si>
-  <si>
     <t>Sterling</t>
   </si>
   <si>
@@ -286,6 +268,18 @@
   </si>
   <si>
     <t>AppplicationSubmitted__c</t>
+  </si>
+  <si>
+    <t>Acknowledgment4__c</t>
+  </si>
+  <si>
+    <t>ApproachMethodology__c</t>
+  </si>
+  <si>
+    <t>Capacity__c</t>
+  </si>
+  <si>
+    <t>Qualifications__c</t>
   </si>
 </sst>
 </file>
@@ -382,9 +376,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -422,7 +416,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -528,7 +522,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -670,7 +664,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -679,11 +673,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="43.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -761,10 +755,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -830,10 +824,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -852,7 +846,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -863,7 +857,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
         <v>30</v>
@@ -874,7 +868,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
         <v>64</v>
@@ -885,7 +879,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
@@ -896,7 +890,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
@@ -910,10 +904,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -932,10 +926,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -943,10 +937,10 @@
         <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -958,10 +952,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1126,10 +1120,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1287,10 +1281,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1323,10 +1317,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.08984375" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1345,7 +1339,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
@@ -1356,7 +1350,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -1371,10 +1365,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1393,7 +1387,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -1404,7 +1398,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -1415,7 +1409,7 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
         <v>30</v>
@@ -1426,7 +1420,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
@@ -1437,7 +1431,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
@@ -1448,7 +1442,7 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
         <v>64</v>
@@ -1463,10 +1457,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093CC3BA-5D8A-4100-9F68-01A898F6AD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E619ED20-A3AD-4F9A-9411-2204D2E5C1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19785" windowHeight="11760" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="83">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Qualifications__c</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -673,11 +676,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -755,10 +758,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -824,10 +827,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -904,10 +907,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -952,10 +955,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1120,10 +1123,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1281,10 +1284,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1317,10 +1320,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="33.08984375" customWidth="1"/>
-    <col min="3" max="3" width="23.453125" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1364,11 +1367,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1406,24 +1409,24 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1431,7 +1434,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
@@ -1442,9 +1445,20 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
         <v>81</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1457,10 +1471,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C54D62-8CC7-469F-B740-F00219C94DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A002584E-B038-4C63-A7D9-2A0D9F0E2C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -1646,10 +1646,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3">

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093CC3BA-5D8A-4100-9F68-01A898F6AD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C51DA8C-A408-453D-842D-2197FCC4C0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="82">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1364,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
@@ -1406,24 +1406,24 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1431,7 +1431,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
@@ -1442,9 +1442,20 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
         <v>81</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>64</v>
       </c>
     </row>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A002584E-B038-4C63-A7D9-2A0D9F0E2C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA0F918-316B-45B5-86F1-CFA5DE37F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -25,17 +25,28 @@
     <sheet name="Form Fields 2" sheetId="5" r:id="rId10"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="179017"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1623,7 +1634,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
@@ -1657,32 +1668,32 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1690,7 +1701,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
@@ -1701,9 +1712,20 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
         <v>81</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>64</v>
       </c>
     </row>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8075E0FA-F368-45F3-A6F6-1AFD783085DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EB93D3-2886-4242-8F39-D54810252898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="89">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -286,6 +286,21 @@
   </si>
   <si>
     <t>City__c</t>
+  </si>
+  <si>
+    <t>Application Project abstract</t>
+  </si>
+  <si>
+    <t>Application Approach Methodology</t>
+  </si>
+  <si>
+    <t>Application Capacity</t>
+  </si>
+  <si>
+    <t>Application Qualifications</t>
+  </si>
+  <si>
+    <t>David Bobs</t>
   </si>
 </sst>
 </file>
@@ -372,9 +387,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -412,7 +427,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -518,7 +533,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -660,7 +675,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -669,11 +684,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -751,10 +766,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -820,10 +835,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -900,10 +915,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -948,10 +963,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1116,10 +1131,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1277,10 +1292,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1313,10 +1328,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1349,7 +1364,7 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1361,10 +1376,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1386,7 +1401,7 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1419,7 +1434,7 @@
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1430,7 +1445,7 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1441,7 +1456,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1453,10 +1468,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA0F918-316B-45B5-86F1-CFA5DE37F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9E60F7-D8B9-4EDD-B298-ABF49864F747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="5" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="91">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -304,6 +304,21 @@
   </si>
   <si>
     <t>Provide an explanation of the qualifications of the personnel as they relate to project objectives.</t>
+  </si>
+  <si>
+    <t>Application Project abstract</t>
+  </si>
+  <si>
+    <t>Application Approach Methodology</t>
+  </si>
+  <si>
+    <t>Application Capacity</t>
+  </si>
+  <si>
+    <t>Application Qualifications</t>
+  </si>
+  <si>
+    <t>David Bobs</t>
   </si>
 </sst>
 </file>
@@ -371,7 +386,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -383,9 +398,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -705,11 +717,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="43.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -787,10 +799,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -934,10 +946,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1003,10 +1015,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1083,10 +1095,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1131,10 +1143,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F95804D-6DD0-4E29-A018-B0CB2E4F2EEA}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="3" width="101.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" customWidth="1"/>
+    <col min="3" max="3" width="101.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1181,14 +1193,14 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13.8" customHeight="1">
+    <row r="5" spans="1:3" ht="13.75" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1199,7 +1211,7 @@
       <c r="B6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1210,7 +1222,7 @@
       <c r="B7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1222,10 +1234,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1390,10 +1402,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1551,10 +1563,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1587,10 +1599,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.08984375" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1608,10 +1620,10 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2">
         <v>0</v>
       </c>
     </row>
@@ -1619,11 +1631,11 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1634,11 +1646,11 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1657,10 +1669,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1668,32 +1680,32 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1701,10 +1713,10 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1712,21 +1724,10 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VA Org 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA0F918-316B-45B5-86F1-CFA5DE37F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1235E8FC-6883-44BD-BF5B-D1345AE8F18F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="87">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t>Provide an explanation of the qualifications of the personnel as they relate to project objectives.</t>
+  </si>
+  <si>
+    <t>Deshka Kostova</t>
   </si>
 </sst>
 </file>
@@ -383,11 +386,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1188,7 +1191,7 @@
       <c r="B5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1199,7 +1202,7 @@
       <c r="B6" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1210,7 +1213,7 @@
       <c r="B7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1600,7 +1603,7 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1608,10 +1611,10 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1619,11 +1622,11 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Va Qa Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA0F918-316B-45B5-86F1-CFA5DE37F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48D8ABB-8F4D-4E8E-AA1C-9F8834D47135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA0F918-316B-45B5-86F1-CFA5DE37F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D258D5E-0E46-418A-9DAA-15C3876D5CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -24,6 +24,8 @@
     <sheet name="Edition" sheetId="2" r:id="rId9"/>
     <sheet name="Form Fields 2" sheetId="5" r:id="rId10"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId11"/>
+    <sheet name="SF424_FORM" sheetId="12" r:id="rId12"/>
+    <sheet name="Sheet3" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="148">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -304,13 +306,199 @@
   </si>
   <si>
     <t>Provide an explanation of the qualifications of the personnel as they relate to project objectives.</t>
+  </si>
+  <si>
+    <t>LegalName__c</t>
+  </si>
+  <si>
+    <t>Automation Test</t>
+  </si>
+  <si>
+    <t>SAMUEI__c</t>
+  </si>
+  <si>
+    <t>Street__c</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>Country__c</t>
+  </si>
+  <si>
+    <t>POC_First_Name__c</t>
+  </si>
+  <si>
+    <t>POC_Last_Name__c</t>
+  </si>
+  <si>
+    <t>(023) 479-9100</t>
+  </si>
+  <si>
+    <t>POC_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>automationspi1@yopmail.com</t>
+  </si>
+  <si>
+    <t>POC_Email__c</t>
+  </si>
+  <si>
+    <t>ApplicantType1__c</t>
+  </si>
+  <si>
+    <t>B: County Government</t>
+  </si>
+  <si>
+    <t>OtherApplicantType__c</t>
+  </si>
+  <si>
+    <t>NameofFederalAgency__c</t>
+  </si>
+  <si>
+    <t>FederalAgency</t>
+  </si>
+  <si>
+    <t>CFDA_Number__c</t>
+  </si>
+  <si>
+    <t>CFDA_Program_Title__c</t>
+  </si>
+  <si>
+    <t>FundingOpportunityTitle__c</t>
+  </si>
+  <si>
+    <t>DescriptiveTitleOfProject__c</t>
+  </si>
+  <si>
+    <t>ApplicantDistrict__c</t>
+  </si>
+  <si>
+    <t>ProgramDistrict__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>FederalFunding__c</t>
+  </si>
+  <si>
+    <t>ApplicantFunding__c</t>
+  </si>
+  <si>
+    <t>StateFunding__c</t>
+  </si>
+  <si>
+    <t>LocalFunding__c</t>
+  </si>
+  <si>
+    <t>OtherFunding__c</t>
+  </si>
+  <si>
+    <t>ProgramIncomeFunding__c</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>POC Prefix</t>
+  </si>
+  <si>
+    <t>POC_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>Mathews</t>
+  </si>
+  <si>
+    <t>SubmissionType__c</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>ApplicationType__c</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>ApplicationReview__c</t>
+  </si>
+  <si>
+    <t>a. This application was made available to the State under the Executive Order 12372 Process for review on</t>
+  </si>
+  <si>
+    <t>FederalDebt__c</t>
+  </si>
+  <si>
+    <t>Agreement__c</t>
+  </si>
+  <si>
+    <t>checked</t>
+  </si>
+  <si>
+    <t>AOR_Prefix__c</t>
+  </si>
+  <si>
+    <t>AOR_First_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Last_Name__c</t>
+  </si>
+  <si>
+    <t>AOR Suffix</t>
+  </si>
+  <si>
+    <t>M.D.</t>
+  </si>
+  <si>
+    <t>AOR_Title__c</t>
+  </si>
+  <si>
+    <t>AOR_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>AOR_Email__c</t>
+  </si>
+  <si>
+    <t>AORSignature__c</t>
+  </si>
+  <si>
+    <t>AORDateSigned__c</t>
+  </si>
+  <si>
+    <t>USA: UNITED STATES</t>
+  </si>
+  <si>
+    <t>Zip_Postal_Code__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,6 +537,12 @@
       <color theme="1"/>
       <name val="Lato"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -371,7 +565,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -389,6 +583,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1000,6 +1195,529 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9CBAEA-81BD-42C3-8AB2-BDBECF06D597}">
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="88.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4">
+        <v>123456789120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C15" r:id="rId1" xr:uid="{3DAE2414-90B6-4989-8EAB-5FCCD8554685}"/>
+    <hyperlink ref="C43" r:id="rId2" xr:uid="{1B061AD1-19A6-4908-9794-0E5FD64175BA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D258D5E-0E46-418A-9DAA-15C3876D5CED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E378288F-3314-41C6-AB71-385B70903B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="148">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -410,9 +410,6 @@
     <t>NY</t>
   </si>
   <si>
-    <t>POC Prefix</t>
-  </si>
-  <si>
     <t>POC_Middle_Name__c</t>
   </si>
   <si>
@@ -467,9 +464,6 @@
     <t>AOR_Last_Name__c</t>
   </si>
   <si>
-    <t>AOR Suffix</t>
-  </si>
-  <si>
     <t>M.D.</t>
   </si>
   <si>
@@ -492,6 +486,12 @@
   </si>
   <si>
     <t>Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>POC_Prefix__c</t>
+  </si>
+  <si>
+    <t>AOR_Suffix__c</t>
   </si>
 </sst>
 </file>
@@ -565,7 +565,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -583,7 +583,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1197,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9CBAEA-81BD-42C3-8AB2-BDBECF06D597}">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -1206,504 +1215,515 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C3" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="14">
+        <v>123456789012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="9">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="9">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="9">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="9">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4">
-        <v>123456789120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5">
+      <c r="C34" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="40" spans="1:3">
+      <c r="A40" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C9">
-        <v>4021</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="C41" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" s="3" t="s">
+    <row r="44" spans="1:3">
+      <c r="A44" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="11" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" t="s">
+    <row r="45" spans="1:3">
+      <c r="A45" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" t="s">
-        <v>105</v>
-      </c>
-      <c r="C20" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C27">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" t="s">
-        <v>117</v>
-      </c>
-      <c r="C32">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" t="s">
-        <v>130</v>
-      </c>
-      <c r="C33" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" t="s">
-        <v>133</v>
-      </c>
-      <c r="C35" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" t="s">
-        <v>136</v>
-      </c>
-      <c r="C37" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" t="s">
-        <v>139</v>
-      </c>
-      <c r="C40" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C42" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="46" spans="1:3">
+      <c r="A46" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" t="s">
-        <v>144</v>
-      </c>
-      <c r="C44" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" t="s">
-        <v>145</v>
-      </c>
-      <c r="C45">
+      <c r="C46" s="9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C15" r:id="rId1" xr:uid="{3DAE2414-90B6-4989-8EAB-5FCCD8554685}"/>
-    <hyperlink ref="C43" r:id="rId2" xr:uid="{1B061AD1-19A6-4908-9794-0E5FD64175BA}"/>
+    <hyperlink ref="C16" r:id="rId1" xr:uid="{70903C96-5C84-4A2C-8D40-A45D77DEA303}"/>
+    <hyperlink ref="C44" r:id="rId2" xr:uid="{EA223F5E-0C67-458D-8B52-67B94FA99AD6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E378288F-3314-41C6-AB71-385B70903B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDF37FB-902D-44A9-9AF3-5885FAF892BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -25,7 +25,8 @@
     <sheet name="Form Fields 2" sheetId="5" r:id="rId10"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId11"/>
     <sheet name="SF424_FORM" sheetId="12" r:id="rId12"/>
-    <sheet name="Sheet3" sheetId="13" r:id="rId13"/>
+    <sheet name="Lobbying_Form" sheetId="13" r:id="rId13"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="152">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -492,13 +493,25 @@
   </si>
   <si>
     <t>AOR_Suffix__c</t>
+  </si>
+  <si>
+    <t>ApplicantsOrganization__c</t>
+  </si>
+  <si>
+    <t>AORContact__c</t>
+  </si>
+  <si>
+    <t>Grantee PO</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,6 +556,12 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -565,7 +584,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -583,16 +602,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1215,508 +1230,508 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="9" t="s">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>127</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="11">
         <v>123456789012</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6">
         <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>75</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="9" t="s">
+      <c r="A9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10">
         <v>4021</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="9" t="s">
+      <c r="A11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="9" t="s">
+      <c r="A12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="13" t="s">
+      <c r="A14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="9" t="s">
+      <c r="A15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="9" t="s">
+      <c r="A16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="9" t="s">
+      <c r="A17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
         <v>99</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="9" t="s">
+      <c r="A18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="9" t="s">
+      <c r="A20" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20">
         <v>1234</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="9" t="s">
+      <c r="A21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="9" t="s">
+      <c r="A22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="9" t="s">
+      <c r="A23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="9" t="s">
+      <c r="A24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
         <v>108</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="9" t="s">
+      <c r="A25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
         <v>109</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="9" t="s">
+      <c r="A26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="9" t="s">
+      <c r="A27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27">
         <v>365</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="9" t="s">
+      <c r="A28" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28">
         <v>10000</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="9" t="s">
+      <c r="A29" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
         <v>113</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29">
         <v>10000</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="13" t="s">
+      <c r="A30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30">
         <v>10000</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="9" t="s">
+      <c r="A31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
         <v>115</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31">
         <v>10000</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="A32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
         <v>116</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32">
         <v>10000</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B33" s="9" t="s">
+      <c r="A33" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
         <v>117</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33">
         <v>10000</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" s="9" t="s">
+      <c r="A34" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B35" s="9" t="s">
+      <c r="A35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
         <v>131</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="9" t="s">
+      <c r="A36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
         <v>132</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="9" t="s">
+      <c r="A37" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B38" s="9" t="s">
+      <c r="A38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
         <v>135</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="9" t="s">
+      <c r="A39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="9" t="s">
+      <c r="A40" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="9" t="s">
+      <c r="A41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
         <v>147</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="13" t="s">
+      <c r="A42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="13" t="s">
+      <c r="A43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="9" t="s">
+      <c r="A44" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" s="9" t="s">
+      <c r="A45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
         <v>142</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="9" t="s">
+      <c r="A46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
         <v>143</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46">
         <v>0</v>
       </c>
     </row>
@@ -1731,6 +1746,120 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.21875" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CDF37FB-902D-44A9-9AF3-5885FAF892BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92D667E-7A4D-4D4C-9F09-397E8ADDC100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -1611,7 +1611,7 @@
         <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:3">

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A92D667E-7A4D-4D4C-9F09-397E8ADDC100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF248E6-40C5-4403-8C58-6D227CFC6EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="13" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId11"/>
     <sheet name="SF424_FORM" sheetId="12" r:id="rId12"/>
     <sheet name="Lobbying_Form" sheetId="13" r:id="rId13"/>
-    <sheet name="Sheet2" sheetId="14" r:id="rId14"/>
+    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="155">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -505,6 +505,15 @@
   </si>
   <si>
     <t>Department of Education</t>
+  </si>
+  <si>
+    <t>Funding_Opportunity_Number__c</t>
+  </si>
+  <si>
+    <t>Applicant_Name__c</t>
+  </si>
+  <si>
+    <t>ProjectSummary__c</t>
   </si>
 </sst>
 </file>
@@ -1860,10 +1869,82 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="28.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA0F918-316B-45B5-86F1-CFA5DE37F9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF248E6-40C5-4403-8C58-6D227CFC6EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="13" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -24,6 +24,9 @@
     <sheet name="Edition" sheetId="2" r:id="rId9"/>
     <sheet name="Form Fields 2" sheetId="5" r:id="rId10"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId11"/>
+    <sheet name="SF424_FORM" sheetId="12" r:id="rId12"/>
+    <sheet name="Lobbying_Form" sheetId="13" r:id="rId13"/>
+    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="155">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -304,13 +307,220 @@
   </si>
   <si>
     <t>Provide an explanation of the qualifications of the personnel as they relate to project objectives.</t>
+  </si>
+  <si>
+    <t>LegalName__c</t>
+  </si>
+  <si>
+    <t>Automation Test</t>
+  </si>
+  <si>
+    <t>SAMUEI__c</t>
+  </si>
+  <si>
+    <t>Street__c</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>Country__c</t>
+  </si>
+  <si>
+    <t>POC_First_Name__c</t>
+  </si>
+  <si>
+    <t>POC_Last_Name__c</t>
+  </si>
+  <si>
+    <t>(023) 479-9100</t>
+  </si>
+  <si>
+    <t>POC_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>automationspi1@yopmail.com</t>
+  </si>
+  <si>
+    <t>POC_Email__c</t>
+  </si>
+  <si>
+    <t>ApplicantType1__c</t>
+  </si>
+  <si>
+    <t>B: County Government</t>
+  </si>
+  <si>
+    <t>OtherApplicantType__c</t>
+  </si>
+  <si>
+    <t>NameofFederalAgency__c</t>
+  </si>
+  <si>
+    <t>FederalAgency</t>
+  </si>
+  <si>
+    <t>CFDA_Number__c</t>
+  </si>
+  <si>
+    <t>CFDA_Program_Title__c</t>
+  </si>
+  <si>
+    <t>FundingOpportunityTitle__c</t>
+  </si>
+  <si>
+    <t>DescriptiveTitleOfProject__c</t>
+  </si>
+  <si>
+    <t>ApplicantDistrict__c</t>
+  </si>
+  <si>
+    <t>ProgramDistrict__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>FederalFunding__c</t>
+  </si>
+  <si>
+    <t>ApplicantFunding__c</t>
+  </si>
+  <si>
+    <t>StateFunding__c</t>
+  </si>
+  <si>
+    <t>LocalFunding__c</t>
+  </si>
+  <si>
+    <t>OtherFunding__c</t>
+  </si>
+  <si>
+    <t>ProgramIncomeFunding__c</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>POC_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>Mathews</t>
+  </si>
+  <si>
+    <t>SubmissionType__c</t>
+  </si>
+  <si>
+    <t>Application</t>
+  </si>
+  <si>
+    <t>ApplicationType__c</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>ApplicationReview__c</t>
+  </si>
+  <si>
+    <t>a. This application was made available to the State under the Executive Order 12372 Process for review on</t>
+  </si>
+  <si>
+    <t>FederalDebt__c</t>
+  </si>
+  <si>
+    <t>Agreement__c</t>
+  </si>
+  <si>
+    <t>checked</t>
+  </si>
+  <si>
+    <t>AOR_Prefix__c</t>
+  </si>
+  <si>
+    <t>AOR_First_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Middle_Name__c</t>
+  </si>
+  <si>
+    <t>AOR_Last_Name__c</t>
+  </si>
+  <si>
+    <t>M.D.</t>
+  </si>
+  <si>
+    <t>AOR_Title__c</t>
+  </si>
+  <si>
+    <t>AOR_Telephone_Number__c</t>
+  </si>
+  <si>
+    <t>AOR_Email__c</t>
+  </si>
+  <si>
+    <t>AORSignature__c</t>
+  </si>
+  <si>
+    <t>AORDateSigned__c</t>
+  </si>
+  <si>
+    <t>USA: UNITED STATES</t>
+  </si>
+  <si>
+    <t>Zip_Postal_Code__c</t>
+  </si>
+  <si>
+    <t>POC_Prefix__c</t>
+  </si>
+  <si>
+    <t>AOR_Suffix__c</t>
+  </si>
+  <si>
+    <t>ApplicantsOrganization__c</t>
+  </si>
+  <si>
+    <t>AORContact__c</t>
+  </si>
+  <si>
+    <t>Grantee PO</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
+  </si>
+  <si>
+    <t>Funding_Opportunity_Number__c</t>
+  </si>
+  <si>
+    <t>Applicant_Name__c</t>
+  </si>
+  <si>
+    <t>ProjectSummary__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,6 +559,18 @@
       <color theme="1"/>
       <name val="Lato"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -371,7 +593,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -389,6 +611,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1000,6 +1228,726 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9CBAEA-81BD-42C3-8AB2-BDBECF06D597}">
+  <dimension ref="A1:C46"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="88.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="11">
+        <v>123456789012</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C16" r:id="rId1" xr:uid="{70903C96-5C84-4A2C-8D40-A45D77DEA303}"/>
+    <hyperlink ref="C44" r:id="rId2" xr:uid="{EA223F5E-0C67-458D-8B52-67B94FA99AD6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="25.5546875" customWidth="1"/>
+    <col min="2" max="2" width="31.21875" customWidth="1"/>
+    <col min="3" max="3" width="25.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="19.88671875" customWidth="1"/>
+    <col min="3" max="3" width="28.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF248E6-40C5-4403-8C58-6D227CFC6EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EC9872-B043-41C8-B043-7811E7067E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="13" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="155">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1230,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9CBAEA-81BD-42C3-8AB2-BDBECF06D597}">
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -1720,28 +1720,6 @@
       </c>
       <c r="C44" s="3" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B45" t="s">
-        <v>142</v>
-      </c>
-      <c r="C45" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" t="s">
-        <v>143</v>
-      </c>
-      <c r="C46">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EC9872-B043-41C8-B043-7811E7067E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCD32AB-3BE7-4022-88CF-1A34AACF67E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="159">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -441,9 +441,6 @@
     <t>ApplicationReview__c</t>
   </si>
   <si>
-    <t>a. This application was made available to the State under the Executive Order 12372 Process for review on</t>
-  </si>
-  <si>
     <t>FederalDebt__c</t>
   </si>
   <si>
@@ -483,9 +480,6 @@
     <t>AORDateSigned__c</t>
   </si>
   <si>
-    <t>USA: UNITED STATES</t>
-  </si>
-  <si>
     <t>Zip_Postal_Code__c</t>
   </si>
   <si>
@@ -514,6 +508,24 @@
   </si>
   <si>
     <t>ProjectSummary__c</t>
+  </si>
+  <si>
+    <t>ND: INDIA</t>
+  </si>
+  <si>
+    <t>ApplicantType2__c</t>
+  </si>
+  <si>
+    <t>ApplicantType3__c</t>
+  </si>
+  <si>
+    <t>A: State Government</t>
+  </si>
+  <si>
+    <t>C: City or Township Government</t>
+  </si>
+  <si>
+    <t>b. Program is subject to E.O. 12372 but has not been selected by the State for review.</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9CBAEA-81BD-42C3-8AB2-BDBECF06D597}">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -1334,7 +1346,7 @@
         <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1342,7 +1354,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C10">
         <v>4021</v>
@@ -1353,7 +1365,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
         <v>121</v>
@@ -1430,10 +1442,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1441,10 +1453,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1452,10 +1464,10 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20">
-        <v>1234</v>
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1463,10 +1475,10 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1474,10 +1486,10 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" t="s">
-        <v>90</v>
+        <v>104</v>
+      </c>
+      <c r="C22">
+        <v>1234</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1485,7 +1497,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C23" t="s">
         <v>90</v>
@@ -1496,7 +1508,7 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C24" t="s">
         <v>90</v>
@@ -1507,7 +1519,7 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C25" t="s">
         <v>90</v>
@@ -1518,10 +1530,10 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1529,10 +1541,10 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27">
-        <v>365</v>
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1540,10 +1552,10 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C28">
-        <v>10000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1551,18 +1563,18 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C29">
-        <v>10000</v>
+        <v>365</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>114</v>
+      <c r="B30" t="s">
+        <v>112</v>
       </c>
       <c r="C30">
         <v>10000</v>
@@ -1573,7 +1585,7 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C31">
         <v>10000</v>
@@ -1583,8 +1595,8 @@
       <c r="A32" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B32" t="s">
-        <v>116</v>
+      <c r="B32" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="C32">
         <v>10000</v>
@@ -1595,7 +1607,7 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33">
         <v>10000</v>
@@ -1606,10 +1618,10 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
-      </c>
-      <c r="C34" t="s">
-        <v>130</v>
+        <v>116</v>
+      </c>
+      <c r="C34">
+        <v>10000</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -1617,10 +1629,10 @@
         <v>4</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35" t="s">
-        <v>39</v>
+        <v>117</v>
+      </c>
+      <c r="C35">
+        <v>10000</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1628,10 +1640,10 @@
         <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1639,10 +1651,10 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1650,10 +1662,10 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1661,10 +1673,10 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1672,10 +1684,10 @@
         <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1683,49 +1695,71 @@
         <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>139</v>
+      <c r="B42" t="s">
+        <v>136</v>
       </c>
       <c r="C42" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>140</v>
+      <c r="B43" t="s">
+        <v>145</v>
       </c>
       <c r="C43" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B44" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="B44" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>97</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C16" r:id="rId1" xr:uid="{70903C96-5C84-4A2C-8D40-A45D77DEA303}"/>
-    <hyperlink ref="C44" r:id="rId2" xr:uid="{EA223F5E-0C67-458D-8B52-67B94FA99AD6}"/>
+    <hyperlink ref="C46" r:id="rId2" xr:uid="{EA223F5E-0C67-458D-8B52-67B94FA99AD6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1757,10 +1791,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1768,10 +1802,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1779,7 +1813,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
         <v>121</v>
@@ -1790,7 +1824,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C5" t="s">
         <v>122</v>
@@ -1801,7 +1835,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
         <v>123</v>
@@ -1812,7 +1846,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
         <v>90</v>
@@ -1823,7 +1857,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C8" t="s">
         <v>90</v>
@@ -1834,7 +1868,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1870,7 +1904,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C2">
         <v>12345</v>
@@ -1892,7 +1926,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
         <v>122</v>
@@ -1914,7 +1948,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
         <v>87</v>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BCD32AB-3BE7-4022-88CF-1A34AACF67E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A674233-417F-4A47-AB4F-158D4A36FC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -510,9 +510,6 @@
     <t>ProjectSummary__c</t>
   </si>
   <si>
-    <t>ND: INDIA</t>
-  </si>
-  <si>
     <t>ApplicantType2__c</t>
   </si>
   <si>
@@ -526,6 +523,9 @@
   </si>
   <si>
     <t>b. Program is subject to E.O. 12372 but has not been selected by the State for review.</t>
+  </si>
+  <si>
+    <t>IND: INDIA</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1346,7 @@
         <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1442,10 +1442,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1453,10 +1453,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1643,7 +1643,7 @@
         <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:3">

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A674233-417F-4A47-AB4F-158D4A36FC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF88379-A6FA-49CE-8335-51457B174132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="8" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="SF424_FORM" sheetId="12" r:id="rId12"/>
     <sheet name="Lobbying_Form" sheetId="13" r:id="rId13"/>
     <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId14"/>
+    <sheet name="Project_Perform_Site" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="174">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -526,13 +527,58 @@
   </si>
   <si>
     <t>IND: INDIA</t>
+  </si>
+  <si>
+    <t>IsPrimaryAddress__c</t>
+  </si>
+  <si>
+    <t>YRNMVN96JC17</t>
+  </si>
+  <si>
+    <t>AddressLine1__c</t>
+  </si>
+  <si>
+    <t>GranteeFormsAddressLine2__c</t>
+  </si>
+  <si>
+    <t>Green filed</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>County__c</t>
+  </si>
+  <si>
+    <t>Adams</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>Province__c</t>
+  </si>
+  <si>
+    <t>NineDigitZipCodeForForms__c</t>
+  </si>
+  <si>
+    <t>12345-5785</t>
+  </si>
+  <si>
+    <t>GranteeFormsCongressionalDistrict__c</t>
+  </si>
+  <si>
+    <t>CR-849</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -583,6 +629,19 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF222222"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -605,7 +664,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -627,8 +686,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1301,8 +1361,8 @@
       <c r="B5" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="11">
-        <v>123456789012</v>
+      <c r="C5" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1790,7 +1850,7 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>146</v>
       </c>
       <c r="C2" t="s">
@@ -1952,6 +2012,135 @@
       </c>
       <c r="C6" t="s">
         <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6A231F-33CA-49C3-B227-66CE20B1151E}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF88379-A6FA-49CE-8335-51457B174132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36150344-7E63-43FF-8D81-8A4686B9E470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="14" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="174">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -2096,6 +2096,9 @@
       </c>
     </row>
     <row r="7" spans="1:3">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
       <c r="B7" s="6" t="s">
         <v>75</v>
       </c>
@@ -2104,6 +2107,9 @@
       </c>
     </row>
     <row r="8" spans="1:3">
+      <c r="A8" s="10" t="s">
+        <v>4</v>
+      </c>
       <c r="B8" s="6" t="s">
         <v>166</v>
       </c>
@@ -2112,6 +2118,9 @@
       </c>
     </row>
     <row r="9" spans="1:3">
+      <c r="A9" s="10" t="s">
+        <v>4</v>
+      </c>
       <c r="B9" s="6" t="s">
         <v>91</v>
       </c>
@@ -2120,6 +2129,9 @@
       </c>
     </row>
     <row r="10" spans="1:3">
+      <c r="A10" s="10" t="s">
+        <v>4</v>
+      </c>
       <c r="B10" s="6" t="s">
         <v>169</v>
       </c>
@@ -2128,6 +2140,9 @@
       </c>
     </row>
     <row r="11" spans="1:3">
+      <c r="A11" s="10" t="s">
+        <v>4</v>
+      </c>
       <c r="B11" s="6" t="s">
         <v>170</v>
       </c>
@@ -2136,10 +2151,13 @@
       </c>
     </row>
     <row r="12" spans="1:3">
+      <c r="A12" s="10" t="s">
+        <v>4</v>
+      </c>
       <c r="B12" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" t="s">
         <v>173</v>
       </c>
     </row>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36150344-7E63-43FF-8D81-8A4686B9E470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D728A90B-B9CB-4840-B215-BDEF724CA949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="14" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D728A90B-B9CB-4840-B215-BDEF724CA949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89533F80-F36F-4A5B-BED8-61FEDE818D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="14" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="171">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -475,12 +475,6 @@
     <t>AOR_Email__c</t>
   </si>
   <si>
-    <t>AORSignature__c</t>
-  </si>
-  <si>
-    <t>AORDateSigned__c</t>
-  </si>
-  <si>
     <t>Zip_Postal_Code__c</t>
   </si>
   <si>
@@ -493,12 +487,6 @@
     <t>ApplicantsOrganization__c</t>
   </si>
   <si>
-    <t>AORContact__c</t>
-  </si>
-  <si>
-    <t>Grantee PO</t>
-  </si>
-  <si>
     <t>Department of Education</t>
   </si>
   <si>
@@ -572,6 +560,9 @@
   </si>
   <si>
     <t>CR-849</t>
+  </si>
+  <si>
+    <t>Jr.</t>
   </si>
 </sst>
 </file>
@@ -1362,7 +1353,7 @@
         <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1406,7 +1397,7 @@
         <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1414,7 +1405,7 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C10">
         <v>4021</v>
@@ -1425,7 +1416,7 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s">
         <v>121</v>
@@ -1502,10 +1493,10 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1513,10 +1504,10 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1703,7 +1694,7 @@
         <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1777,7 +1768,7 @@
         <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C43" t="s">
         <v>137</v>
@@ -1827,7 +1818,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.5546875" customWidth="1"/>
@@ -1851,10 +1842,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1862,10 +1853,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1873,10 +1864,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1884,21 +1875,21 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
+      <c r="B6" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1912,30 +1903,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1964,7 +1934,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C2">
         <v>12345</v>
@@ -1986,7 +1956,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
         <v>122</v>
@@ -2008,7 +1978,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C6" t="s">
         <v>87</v>
@@ -2056,7 +2026,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -2070,7 +2040,7 @@
         <v>88</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2078,10 +2048,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2089,10 +2059,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2103,7 +2073,7 @@
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2111,10 +2081,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2125,7 +2095,7 @@
         <v>91</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2133,7 +2103,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
         <v>90</v>
@@ -2144,10 +2114,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2155,10 +2125,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C12" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89533F80-F36F-4A5B-BED8-61FEDE818D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25A4F62-AD5F-46D7-A0B7-86A9FE5090FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="14" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -526,9 +526,6 @@
     <t>AddressLine1__c</t>
   </si>
   <si>
-    <t>GranteeFormsAddressLine2__c</t>
-  </si>
-  <si>
     <t>Green filed</t>
   </si>
   <si>
@@ -563,6 +560,9 @@
   </si>
   <si>
     <t>Jr.</t>
+  </si>
+  <si>
+    <t>AddressLine2__c</t>
   </si>
 </sst>
 </file>
@@ -1889,7 +1889,7 @@
         <v>143</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2051,7 +2051,7 @@
         <v>157</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2059,10 +2059,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" t="s">
-        <v>160</v>
+        <v>170</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2073,7 +2073,7 @@
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2081,10 +2081,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2095,7 +2095,7 @@
         <v>91</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2103,7 +2103,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C10" t="s">
         <v>90</v>
@@ -2114,10 +2114,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" t="s">
         <v>166</v>
-      </c>
-      <c r="C11" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2125,10 +2125,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" t="s">
         <v>168</v>
-      </c>
-      <c r="C12" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Va Qa Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48D8ABB-8F4D-4E8E-AA1C-9F8834D47135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0087AC-8E01-4C66-AF4F-DF709DDD21F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="4" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="96">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -282,35 +282,65 @@
     <t>AppplicationSubmitted__c</t>
   </si>
   <si>
+    <t>ApproachMethodology__c</t>
+  </si>
+  <si>
+    <t>Capacity__c</t>
+  </si>
+  <si>
+    <t>Qualifications__c</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Provide an explanation of the approach and methodology that will be used to meet the project objectives.</t>
+  </si>
+  <si>
+    <t>Provide an explanation of the capacity of the organization to meet the project objectives.</t>
+  </si>
+  <si>
+    <t>Provide an explanation of the qualifications of the personnel as they relate to project objectives.</t>
+  </si>
+  <si>
+    <t>Addressline2__c</t>
+  </si>
+  <si>
+    <t>Street1</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>County__c</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>Zip4__c</t>
+  </si>
+  <si>
+    <t>CongressionalDistrict1__c</t>
+  </si>
+  <si>
+    <t>GranteeProgramincome__c</t>
+  </si>
+  <si>
     <t>Acknowledgment4__c</t>
-  </si>
-  <si>
-    <t>ApproachMethodology__c</t>
-  </si>
-  <si>
-    <t>Capacity__c</t>
-  </si>
-  <si>
-    <t>Qualifications__c</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Provide an explanation of the approach and methodology that will be used to meet the project objectives.</t>
-  </si>
-  <si>
-    <t>Provide an explanation of the capacity of the organization to meet the project objectives.</t>
-  </si>
-  <si>
-    <t>Provide an explanation of the qualifications of the personnel as they relate to project objectives.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,6 +379,12 @@
       <color theme="1"/>
       <name val="Lato"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -371,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -388,6 +424,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1047,7 +1087,7 @@
         <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>64</v>
@@ -1058,7 +1098,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
@@ -1069,7 +1109,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
@@ -1178,7 +1218,7 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="13.8" customHeight="1">
@@ -1186,10 +1226,10 @@
         <v>63</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1197,10 +1237,10 @@
         <v>63</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1208,10 +1248,10 @@
         <v>63</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1634,7 +1674,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
@@ -1668,10 +1708,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1679,54 +1719,87 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
+        <v>93</v>
+      </c>
+      <c r="C7">
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
+        <v>92</v>
+      </c>
+      <c r="C8" s="10">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="10">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25A4F62-AD5F-46D7-A0B7-86A9FE5090FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FF782C-1AB4-4F8D-9EEC-D473F47B77F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="14" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -562,7 +562,7 @@
     <t>Jr.</t>
   </si>
   <si>
-    <t>AddressLine2__c</t>
+    <t>GranteeFormsAddressLine2__c</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FF782C-1AB4-4F8D-9EEC-D473F47B77F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB3463F-94F6-4BDF-92B1-D2CAB8A90E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="14" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="172">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -563,6 +563,9 @@
   </si>
   <si>
     <t>GranteeFormsAddressLine2__c</t>
+  </si>
+  <si>
+    <t>Phillips</t>
   </si>
 </sst>
 </file>
@@ -1818,7 +1821,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25.5546875" customWidth="1"/>
@@ -1875,31 +1878,42 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>169</v>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
         <v>138</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>90</v>
       </c>
     </row>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NonFedDemoCreation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB3463F-94F6-4BDF-92B1-D2CAB8A90E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4686A7B4-5C4A-47F4-850E-43EDDCFC0CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="7" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="172">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -2785,7 +2785,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
@@ -2808,10 +2808,10 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2819,32 +2819,32 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2852,7 +2852,7 @@
         <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
         <v>64</v>
@@ -2863,20 +2863,9 @@
         <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" t="s">
         <v>64</v>
       </c>
     </row>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB3463F-94F6-4BDF-92B1-D2CAB8A90E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF10DBEC-A4BC-4F5D-A4F4-F6EE1F26DF75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="13" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GovGrants Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB3463F-94F6-4BDF-92B1-D2CAB8A90E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822F00CB-9D7F-459F-9D2A-E027A634AC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="9" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -25,9 +25,10 @@
     <sheet name="Form Fields 2" sheetId="5" r:id="rId10"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId11"/>
     <sheet name="SF424_FORM" sheetId="12" r:id="rId12"/>
-    <sheet name="Lobbying_Form" sheetId="13" r:id="rId13"/>
-    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId14"/>
-    <sheet name="Project_Perform_Site" sheetId="15" r:id="rId15"/>
+    <sheet name="SF424FormFederalDebt" sheetId="16" r:id="rId13"/>
+    <sheet name="Lobbying_Form" sheetId="13" r:id="rId14"/>
+    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId15"/>
+    <sheet name="Project_Perform_Site" sheetId="15" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="172">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -999,11 +1000,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="43.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1081,10 +1082,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1228,10 +1229,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1297,11 +1298,11 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9CBAEA-81BD-42C3-8AB2-BDBECF06D597}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="88.77734375" customWidth="1"/>
+    <col min="3" max="3" width="88.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1820,13 +1821,13 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEC6A32-DB67-4C3E-B8E3-D98D49387974}">
+  <dimension ref="A1:C46"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.21875" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="88.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1841,95 +1842,517 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>144</v>
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
         <v>133</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C39" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="40" spans="1:3">
+      <c r="A40" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
         <v>134</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C40" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="41" spans="1:3">
+      <c r="A41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
         <v>135</v>
       </c>
-      <c r="C5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
         <v>136</v>
       </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="C42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C43" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C44" t="s">
         <v>90</v>
       </c>
     </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C16" r:id="rId1" xr:uid="{68F3C995-FDD6-41AA-A91F-5E27CC1F120A}"/>
+    <hyperlink ref="C46" r:id="rId2" xr:uid="{EACAD1DF-70D9-4A93-A9FD-C885B813C10E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="28.21875" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.1796875" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1944,58 +2367,80 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C2">
-        <v>12345</v>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3">
-        <v>1234</v>
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>147</v>
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>134</v>
       </c>
       <c r="C4" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>107</v>
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>135</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>148</v>
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2005,12 +2450,93 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="19.90625" customWidth="1"/>
+    <col min="3" max="3" width="28.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6A231F-33CA-49C3-B227-66CE20B1151E}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2154,10 +2680,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2234,10 +2760,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2282,10 +2808,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F95804D-6DD0-4E29-A018-B0CB2E4F2EEA}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="3" width="101.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" customWidth="1"/>
+    <col min="3" max="3" width="101.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2332,7 +2858,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13.8" customHeight="1">
+    <row r="5" spans="1:3" ht="13.75" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>63</v>
       </c>
@@ -2373,10 +2899,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2541,10 +3067,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2702,10 +3228,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2738,10 +3264,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.08984375" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2786,10 +3312,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Merge_Org_Proj\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB3463F-94F6-4BDF-92B1-D2CAB8A90E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BA123E-5AF9-4C53-969A-617DE20FDDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,13 @@
     <sheet name="Creation" sheetId="1" r:id="rId7"/>
     <sheet name="Form Fields 1" sheetId="4" r:id="rId8"/>
     <sheet name="Edition" sheetId="2" r:id="rId9"/>
-    <sheet name="Form Fields 2" sheetId="5" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId11"/>
-    <sheet name="SF424_FORM" sheetId="12" r:id="rId12"/>
-    <sheet name="Lobbying_Form" sheetId="13" r:id="rId13"/>
-    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId14"/>
-    <sheet name="Project_Perform_Site" sheetId="15" r:id="rId15"/>
+    <sheet name="Edition_userRegister" sheetId="16" r:id="rId10"/>
+    <sheet name="Form Fields 2" sheetId="5" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId12"/>
+    <sheet name="SF424_FORM" sheetId="12" r:id="rId13"/>
+    <sheet name="Lobbying_Form" sheetId="13" r:id="rId14"/>
+    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId15"/>
+    <sheet name="Project_Perform_Site" sheetId="15" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="172">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -999,11 +1000,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="43.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1079,12 +1080,103 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56136D54-D201-4F1B-8E74-02F8225F1896}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1225,13 +1317,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1294,14 +1386,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9CBAEA-81BD-42C3-8AB2-BDBECF06D597}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="88.77734375" customWidth="1"/>
+    <col min="3" max="3" width="88.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1819,14 +1911,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="25.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.21875" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" customWidth="1"/>
+    <col min="1" max="1" width="25.54296875" customWidth="1"/>
+    <col min="2" max="2" width="31.1796875" customWidth="1"/>
+    <col min="3" max="3" width="25.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1915,87 +2007,6 @@
       </c>
       <c r="C8" t="s">
         <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="28.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C2">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2005,12 +2016,93 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="19.90625" customWidth="1"/>
+    <col min="3" max="3" width="28.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6A231F-33CA-49C3-B227-66CE20B1151E}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2154,10 +2246,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2234,10 +2326,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2282,10 +2374,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F95804D-6DD0-4E29-A018-B0CB2E4F2EEA}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="3" width="101.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" customWidth="1"/>
+    <col min="3" max="3" width="101.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2332,7 +2424,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13.8" customHeight="1">
+    <row r="5" spans="1:3" ht="13.75" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>63</v>
       </c>
@@ -2373,10 +2465,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2541,10 +2633,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2702,10 +2794,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2738,10 +2830,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.08984375" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2786,10 +2878,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\cleanupksde\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB3463F-94F6-4BDF-92B1-D2CAB8A90E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A047472-464D-4419-ACD2-FC29337F888F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -999,11 +999,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC0ED488-2B1F-4F16-8235-EEBCD02879E6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1081,10 +1081,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E5D97A-D013-4183-BB17-5426A6B81276}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="76.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="76.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1228,10 +1228,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1297,11 +1297,11 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9CBAEA-81BD-42C3-8AB2-BDBECF06D597}">
   <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="88.77734375" customWidth="1"/>
+    <col min="3" max="3" width="88.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1822,11 +1822,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="25.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.21875" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" customWidth="1"/>
+    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1926,10 +1926,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.88671875" customWidth="1"/>
-    <col min="3" max="3" width="28.21875" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2007,10 +2007,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6A231F-33CA-49C3-B227-66CE20B1151E}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2154,10 +2154,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766848EE-2835-4541-A2DE-2EBCDE357668}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2234,10 +2234,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16F34EE-937B-4D9C-AA9F-266997B4D30C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2282,10 +2282,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F95804D-6DD0-4E29-A018-B0CB2E4F2EEA}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="3" width="101.109375" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
+    <col min="3" max="3" width="101.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2332,7 +2332,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13.8" customHeight="1">
+    <row r="5" spans="1:3" ht="13.9" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>63</v>
       </c>
@@ -2373,10 +2373,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4273BE-F829-4298-BC03-1F37623C37B1}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2541,10 +2541,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A408404E-903C-4747-8B93-C5CB9A3B0B16}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2702,10 +2702,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2738,10 +2738,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2428A64E-9297-4AA1-BA48-EB8E69A06CF3}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2786,10 +2786,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A097844-34E4-4BE1-AA5B-8A6518D2ECB3}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="44.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Merge_Org_Proj\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BA123E-5AF9-4C53-969A-617DE20FDDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A5DBFF-E547-42FF-B741-ABC68834530F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="10" activeTab="13" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Editionpre-app" sheetId="6" r:id="rId1"/>
@@ -26,9 +26,10 @@
     <sheet name="Form Fields 2" sheetId="5" r:id="rId11"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId12"/>
     <sheet name="SF424_FORM" sheetId="12" r:id="rId13"/>
-    <sheet name="Lobbying_Form" sheetId="13" r:id="rId14"/>
-    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId15"/>
-    <sheet name="Project_Perform_Site" sheetId="15" r:id="rId16"/>
+    <sheet name="SF424FormFederalDebt" sheetId="17" r:id="rId14"/>
+    <sheet name="Lobbying_Form" sheetId="13" r:id="rId15"/>
+    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId16"/>
+    <sheet name="Project_Perform_Site" sheetId="15" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="172">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1912,6 +1913,530 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE2B930-9671-40BB-894E-1C9FCA3A454A}">
+  <dimension ref="A1:C46"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>112</v>
+      </c>
+      <c r="C30">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>116</v>
+      </c>
+      <c r="C34">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>133</v>
+      </c>
+      <c r="C39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>134</v>
+      </c>
+      <c r="C40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C16" r:id="rId1" xr:uid="{03ACE2AC-297B-46DB-B554-33397AF80A4F}"/>
+    <hyperlink ref="C46" r:id="rId2" xr:uid="{8DAFBC95-4DBA-4237-9716-4DD3953D310B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -2015,7 +2540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -2096,7 +2621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6A231F-33CA-49C3-B227-66CE20B1151E}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5"/>

--- a/src/main/resources/Application_Field_Values.xlsx
+++ b/src/main/resources/Application_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Merge_Org_Proj\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A5DBFF-E547-42FF-B741-ABC68834530F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68897AAB-DE67-4AE6-806E-A635EA453D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="10" activeTab="13" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
@@ -26,10 +26,11 @@
     <sheet name="Form Fields 2" sheetId="5" r:id="rId11"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId12"/>
     <sheet name="SF424_FORM" sheetId="12" r:id="rId13"/>
-    <sheet name="SF424FormFederalDebt" sheetId="17" r:id="rId14"/>
-    <sheet name="Lobbying_Form" sheetId="13" r:id="rId15"/>
-    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId16"/>
-    <sheet name="Project_Perform_Site" sheetId="15" r:id="rId17"/>
+    <sheet name="SF424_FORM1" sheetId="18" r:id="rId14"/>
+    <sheet name="SF424FormFederalDebt" sheetId="17" r:id="rId15"/>
+    <sheet name="Lobbying_Form" sheetId="13" r:id="rId16"/>
+    <sheet name="Project_Abstract_Summary" sheetId="14" r:id="rId17"/>
+    <sheet name="Project_Perform_Site" sheetId="15" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="172">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1913,6 +1914,497 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A6EB291-DC27-4664-BC15-DF21BDD29372}">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>134</v>
+      </c>
+      <c r="C37" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>143</v>
+      </c>
+      <c r="C40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>140</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C13" r:id="rId1" xr:uid="{4224199A-87D6-4770-B2E1-ACB0C2EBD6C6}"/>
+    <hyperlink ref="C43" r:id="rId2" xr:uid="{6DA0C2CB-0DE8-43F1-8B91-AC50D9FEF40C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAE2B930-9671-40BB-894E-1C9FCA3A454A}">
   <dimension ref="A1:C46"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -2436,7 +2928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D28E1E7-FC4C-4900-90AA-C7AF1D9F0A82}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -2540,7 +3032,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD1E1DC0-0C8E-449D-A28A-32E1162B4081}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -2621,7 +3113,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D6A231F-33CA-49C3-B227-66CE20B1151E}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
